--- a/base_datas/mediana_porte_detalhamento.xlsx
+++ b/base_datas/mediana_porte_detalhamento.xlsx
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>450.6256326690304</v>
+        <v>456.8052171301064</v>
       </c>
       <c r="C2">
-        <v>93.85868977928376</v>
+        <v>94.31042408685016</v>
       </c>
       <c r="D2">
-        <v>6160.006504565668</v>
+        <v>6161.294600689007</v>
       </c>
       <c r="E2">
-        <v>203.6991251476329</v>
+        <v>203.7636758271807</v>
       </c>
       <c r="F2">
-        <v>417.6053922671344</v>
+        <v>419.6955285812672</v>
       </c>
       <c r="G2">
-        <v>26.74412764194565</v>
+        <v>26.79082506422203</v>
       </c>
       <c r="H2">
-        <v>2.464289194246486</v>
+        <v>2.44279792746114</v>
       </c>
       <c r="I2">
-        <v>193.6979540567158</v>
+        <v>194.5469730910116</v>
       </c>
       <c r="J2">
         <v>54.05462622262287</v>
       </c>
       <c r="K2">
-        <v>6.542456719352234E-15</v>
+        <v>6.521866769015956E-15</v>
       </c>
       <c r="L2">
-        <v>3668.231330543728</v>
+        <v>3671.029392642839</v>
       </c>
       <c r="M2">
-        <v>1198.665492033857</v>
+        <v>1204.829392165691</v>
       </c>
       <c r="N2">
-        <v>1038.276592869498</v>
+        <v>1038.575232673646</v>
       </c>
       <c r="O2">
-        <v>133.3601325301205</v>
+        <v>133.5732065940366</v>
       </c>
       <c r="P2">
-        <v>10.33738650999623</v>
+        <v>10.5693961830617</v>
       </c>
       <c r="Q2">
-        <v>0.5236530226073101</v>
+        <v>0.4984936514551702</v>
       </c>
       <c r="R2">
         <v>7.332765104418089</v>
       </c>
       <c r="S2">
-        <v>22.99870697543174</v>
+        <v>23.01537716715766</v>
       </c>
       <c r="T2">
-        <v>26.4244898336414</v>
+        <v>27.14053595953406</v>
       </c>
       <c r="U2">
-        <v>26.703024573251</v>
+        <v>27.06993996826654</v>
       </c>
       <c r="V2">
-        <v>145.6032552932305</v>
+        <v>146.2342165631187</v>
       </c>
       <c r="W2">
-        <v>172.5681165708563</v>
+        <v>172.7555519555659</v>
       </c>
       <c r="Z2">
-        <v>1.580777606904791E-14</v>
+        <v>1.57042117667523E-14</v>
       </c>
       <c r="AA2">
-        <v>12.78764122217556</v>
+        <v>12.70860236705915</v>
       </c>
       <c r="AB2">
-        <v>14.34896476224583</v>
+        <v>14.44503481508766</v>
       </c>
       <c r="AC2">
-        <v>8.818282974494701E-17</v>
+        <v>1.133679902490406E-16</v>
       </c>
       <c r="AD2">
-        <v>1.116777786746307</v>
+        <v>1.037030797101449</v>
       </c>
       <c r="AE2">
-        <v>8.000536172695449</v>
+        <v>8.853856460638839</v>
       </c>
       <c r="AF2">
         <v>27.7285557212076</v>
       </c>
       <c r="AG2">
-        <v>0.2170091418460631</v>
+        <v>0.2177627074897195</v>
       </c>
       <c r="AH2">
-        <v>2270.069233558672</v>
+        <v>2274.423401747882</v>
       </c>
       <c r="AJ2">
-        <v>43.97884586768421</v>
+        <v>43.98790602108272</v>
       </c>
       <c r="AK2">
-        <v>630.9461879494374</v>
+        <v>630.4247320461352</v>
       </c>
       <c r="AL2">
-        <v>116.7171192429247</v>
+        <v>116.7422103556785</v>
       </c>
       <c r="AM2">
-        <v>222.4197080774844</v>
+        <v>220.41225745206</v>
       </c>
       <c r="AN2">
-        <v>28.53491282957244</v>
+        <v>28.48400306997056</v>
       </c>
       <c r="AO2">
-        <v>50.82110666362606</v>
+        <v>51.04342032892968</v>
       </c>
       <c r="AP2">
-        <v>835.275786531667</v>
+        <v>835.4487473987347</v>
       </c>
       <c r="AQ2">
-        <v>82.37278227755047</v>
+        <v>83.30802230242037</v>
       </c>
       <c r="AR2">
-        <v>55.19440006139949</v>
+        <v>55.26116707078228</v>
       </c>
       <c r="AS2">
-        <v>9.938647058136137</v>
+        <v>9.935197282466683</v>
       </c>
       <c r="AT2">
         <v>3.748675733715104</v>
       </c>
       <c r="AU2">
-        <v>84.344921469453</v>
+        <v>84.70313406351686</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,46 +742,46 @@
         </is>
       </c>
       <c r="B3">
-        <v>1151.697488855529</v>
+        <v>1147.647611721434</v>
       </c>
       <c r="C3">
-        <v>229.2950446271612</v>
+        <v>228.0856205795863</v>
       </c>
       <c r="D3">
-        <v>3943.36987080005</v>
+        <v>3931.003989683961</v>
       </c>
       <c r="E3">
-        <v>444.7050963348964</v>
+        <v>439.214179733445</v>
       </c>
       <c r="F3">
-        <v>1021.207905932012</v>
+        <v>1013.232356311615</v>
       </c>
       <c r="G3">
         <v>79.58381908443897</v>
       </c>
       <c r="H3">
-        <v>0.5193485026561986</v>
+        <v>0.5180636711062901</v>
       </c>
       <c r="I3">
-        <v>157.2140538182077</v>
+        <v>156.2716555857762</v>
       </c>
       <c r="J3">
-        <v>88.03507828112672</v>
+        <v>88.2848482646687</v>
       </c>
       <c r="K3">
-        <v>-5.392937609604782E-15</v>
+        <v>-5.096017852569286E-15</v>
       </c>
       <c r="L3">
-        <v>1828.040776081521</v>
+        <v>1827.630779564254</v>
       </c>
       <c r="M3">
-        <v>1179.783139226421</v>
+        <v>1178.68281687783</v>
       </c>
       <c r="N3">
-        <v>809.0276161597283</v>
+        <v>809.1895796967893</v>
       </c>
       <c r="O3">
-        <v>213.6648455737482</v>
+        <v>209.6474237182563</v>
       </c>
       <c r="P3">
         <v>19.31889854378154</v>
@@ -793,34 +793,34 @@
         <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>98.88162806599524</v>
+        <v>96.12903027292657</v>
       </c>
       <c r="T3">
-        <v>245.0038390182517</v>
+        <v>241.9893683254195</v>
       </c>
       <c r="U3">
         <v>87.63185848747365</v>
       </c>
       <c r="V3">
-        <v>401.3171496322813</v>
+        <v>400.2408040363246</v>
       </c>
       <c r="W3">
-        <v>224.234212003079</v>
+        <v>223.2068780457181</v>
       </c>
       <c r="Z3">
-        <v>1.786744253348704E-14</v>
+        <v>1.501599823540043E-14</v>
       </c>
       <c r="AA3">
-        <v>33.75429208975805</v>
+        <v>33.80549900875715</v>
       </c>
       <c r="AB3">
-        <v>44.29964367913524</v>
+        <v>44.98823237315375</v>
       </c>
       <c r="AC3">
-        <v>-8.94031958376621E-16</v>
+        <v>-8.036457646879711E-16</v>
       </c>
       <c r="AD3">
-        <v>0.318141573043313</v>
+        <v>0.2991744770552943</v>
       </c>
       <c r="AE3">
         <v>2.006940626276107</v>
@@ -832,16 +832,16 @@
         <v>0.09331548013676666</v>
       </c>
       <c r="AH3">
-        <v>942.7559345996278</v>
+        <v>940.6839533742919</v>
       </c>
       <c r="AJ3">
-        <v>24.16460223138653</v>
+        <v>24.32261728719821</v>
       </c>
       <c r="AK3">
         <v>475.0941768305947</v>
       </c>
       <c r="AL3">
-        <v>76.73700512961436</v>
+        <v>76.87468518865045</v>
       </c>
       <c r="AM3">
         <v>28.63272351474025</v>
@@ -850,25 +850,25 @@
         <v>12.14586612392583</v>
       </c>
       <c r="AO3">
-        <v>19.8401654264599</v>
+        <v>19.40583099832969</v>
       </c>
       <c r="AP3">
         <v>766.8603074847499</v>
       </c>
       <c r="AQ3">
-        <v>213.7064350395914</v>
+        <v>213.5049392633443</v>
       </c>
       <c r="AR3">
-        <v>69.17810064424573</v>
+        <v>66.86292147758216</v>
       </c>
       <c r="AS3">
         <v>5.473453749315818</v>
       </c>
       <c r="AT3">
-        <v>2.376402405279721</v>
+        <v>2.384712271618399</v>
       </c>
       <c r="AU3">
-        <v>44.07059171268155</v>
+        <v>43.54038668085465</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>583.6242487943942</v>
+        <v>580.386420385051</v>
       </c>
       <c r="C4">
-        <v>124.0111320595555</v>
+        <v>124.8018128491161</v>
       </c>
       <c r="D4">
         <v>5232.048112211221</v>
       </c>
       <c r="E4">
-        <v>231.7837004548408</v>
+        <v>230.7162991983168</v>
       </c>
       <c r="F4">
-        <v>520.2307359202779</v>
+        <v>518.2245071081182</v>
       </c>
       <c r="G4">
-        <v>38.30543527071195</v>
+        <v>38.22514492373747</v>
       </c>
       <c r="H4">
-        <v>1.05080322702753</v>
+        <v>0.9839431652480586</v>
       </c>
       <c r="I4">
-        <v>187.9667100737101</v>
+        <v>188.6548454394294</v>
       </c>
       <c r="J4">
-        <v>66.01950500935814</v>
+        <v>66.40653266897502</v>
       </c>
       <c r="K4">
-        <v>6.352467632158398E-15</v>
+        <v>6.427150370866544E-15</v>
       </c>
       <c r="L4">
-        <v>3020.004460313193</v>
+        <v>3020.398339020229</v>
       </c>
       <c r="M4">
-        <v>1120.83774184834</v>
+        <v>1119.91407261957</v>
       </c>
       <c r="N4">
-        <v>977.0115791949789</v>
+        <v>978.8122197183047</v>
       </c>
       <c r="O4">
         <v>135.3977475710441</v>
       </c>
       <c r="P4">
-        <v>11.49564814003266</v>
+        <v>11.62278054391974</v>
       </c>
       <c r="Q4">
-        <v>0.7357870518609986</v>
+        <v>0.8105006954102921</v>
       </c>
       <c r="R4">
         <v>6.657107266695567</v>
       </c>
       <c r="S4">
-        <v>34.07317088286418</v>
+        <v>33.64501094777414</v>
       </c>
       <c r="T4">
-        <v>65.59527172763798</v>
+        <v>65.35693118091348</v>
       </c>
       <c r="U4">
-        <v>39.0331010994409</v>
+        <v>38.87635186936825</v>
       </c>
       <c r="V4">
-        <v>195.0747659498717</v>
+        <v>197.1188569344294</v>
       </c>
       <c r="W4">
-        <v>181.7019049196011</v>
+        <v>182.1734382069369</v>
       </c>
       <c r="Z4">
-        <v>1.948425238244579E-14</v>
+        <v>1.943819032007594E-14</v>
       </c>
       <c r="AA4">
         <v>19.61055887531345</v>
       </c>
       <c r="AB4">
-        <v>15.12169004693073</v>
+        <v>15.11280281375059</v>
       </c>
       <c r="AC4">
-        <v>-3.290819308807874E-17</v>
+        <v>-3.428732599056737E-17</v>
       </c>
       <c r="AD4">
-        <v>0.7809675478866551</v>
+        <v>0.7552765047539882</v>
       </c>
       <c r="AE4">
-        <v>0.2732647625291972</v>
+        <v>0.2426351921111595</v>
       </c>
       <c r="AF4">
-        <v>27.29024809152821</v>
+        <v>28.39939251345966</v>
       </c>
       <c r="AG4">
-        <v>0.1145514632476978</v>
+        <v>0.1117478923236208</v>
       </c>
       <c r="AH4">
-        <v>1637.631278806614</v>
+        <v>1636.375904583421</v>
       </c>
       <c r="AJ4">
         <v>34.06684321123263</v>
       </c>
       <c r="AK4">
-        <v>573.9121039858803</v>
+        <v>573.89764619011</v>
       </c>
       <c r="AL4">
-        <v>111.3065775303098</v>
+        <v>111.3839913608092</v>
       </c>
       <c r="AM4">
-        <v>223.0083036835496</v>
+        <v>226.1456490372054</v>
       </c>
       <c r="AN4">
-        <v>23.78472302960183</v>
+        <v>23.76877110530896</v>
       </c>
       <c r="AO4">
-        <v>37.31255486423841</v>
+        <v>37.99963305581243</v>
       </c>
       <c r="AP4">
-        <v>706.1995342774608</v>
+        <v>704.9803686393028</v>
       </c>
       <c r="AQ4">
-        <v>110.2971352872312</v>
+        <v>110.1496161609506</v>
       </c>
       <c r="AR4">
         <v>52.12223544712884</v>
       </c>
       <c r="AS4">
-        <v>8.090145085803432</v>
+        <v>8.108818213568497</v>
       </c>
       <c r="AT4">
-        <v>4.242347816781932</v>
+        <v>4.035897375728421</v>
       </c>
       <c r="AU4">
-        <v>68.13251346564036</v>
+        <v>67.9829424124059</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1159,49 +1159,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>523.6222290747421</v>
+        <v>526.5798574022358</v>
       </c>
       <c r="C6">
-        <v>84.36839850295289</v>
+        <v>84.49251608762253</v>
       </c>
       <c r="D6">
-        <v>7154.229862351052</v>
+        <v>7159.541265060934</v>
       </c>
       <c r="E6">
         <v>256.471443954926</v>
       </c>
       <c r="F6">
-        <v>467.2377202102275</v>
+        <v>469.2098129329008</v>
       </c>
       <c r="G6">
-        <v>31.65709835856308</v>
+        <v>31.72372854464157</v>
       </c>
       <c r="H6">
-        <v>4.485234944788139</v>
+        <v>4.573460383362967</v>
       </c>
       <c r="I6">
-        <v>227.5981179885025</v>
+        <v>229.1052123604165</v>
       </c>
       <c r="J6">
-        <v>54.81680948687411</v>
+        <v>54.81439366160294</v>
       </c>
       <c r="K6">
-        <v>7.146073431570305E-15</v>
+        <v>7.046079277746932E-15</v>
       </c>
       <c r="L6">
-        <v>4194.763232427769</v>
+        <v>4202.518794059943</v>
       </c>
       <c r="M6">
         <v>1754.655872245822</v>
       </c>
       <c r="N6">
-        <v>1014.167335362479</v>
+        <v>1014.609145366365</v>
       </c>
       <c r="O6">
-        <v>174.5055130731807</v>
+        <v>173.7867821307229</v>
       </c>
       <c r="P6">
-        <v>17.44562173331713</v>
+        <v>17.38879683704048</v>
       </c>
       <c r="Q6">
         <v>2.999543751511336</v>
@@ -1210,64 +1210,64 @@
         <v>9.454290137911215</v>
       </c>
       <c r="S6">
-        <v>22.82782238305218</v>
+        <v>22.87875887533407</v>
       </c>
       <c r="T6">
-        <v>40.19492581919095</v>
+        <v>39.73896531010663</v>
       </c>
       <c r="U6">
-        <v>49.26645631769541</v>
+        <v>49.62751759446168</v>
       </c>
       <c r="V6">
-        <v>149.0587425950698</v>
+        <v>149.7876765466481</v>
       </c>
       <c r="W6">
-        <v>176.9724412206224</v>
+        <v>176.8629393767401</v>
       </c>
       <c r="Z6">
-        <v>1.611285502847868E-14</v>
+        <v>1.612400579320427E-14</v>
       </c>
       <c r="AA6">
-        <v>11.74109880289519</v>
+        <v>11.86143283938815</v>
       </c>
       <c r="AB6">
-        <v>19.06558734423207</v>
+        <v>19.03994575045208</v>
       </c>
       <c r="AC6">
-        <v>-1.542635869397706E-17</v>
+        <v>-3.980631572885715E-18</v>
       </c>
       <c r="AD6">
-        <v>2.713943778512221</v>
+        <v>2.7193970856102</v>
       </c>
       <c r="AE6">
         <v>6.370504097726922</v>
       </c>
       <c r="AF6">
-        <v>33.46588557345914</v>
+        <v>34.20417873651772</v>
       </c>
       <c r="AG6">
         <v>0.441501789781972</v>
       </c>
       <c r="AH6">
-        <v>2798.072175975</v>
+        <v>2799.755190593401</v>
       </c>
       <c r="AJ6">
-        <v>54.68343238668422</v>
+        <v>54.84975469647571</v>
       </c>
       <c r="AK6">
-        <v>621.5323996649465</v>
+        <v>622.9725749243162</v>
       </c>
       <c r="AL6">
-        <v>106.5805140286088</v>
+        <v>106.7910959314772</v>
       </c>
       <c r="AM6">
-        <v>71.8504468738013</v>
+        <v>72.03521308576481</v>
       </c>
       <c r="AN6">
-        <v>36.91147952663471</v>
+        <v>37.16310449268046</v>
       </c>
       <c r="AO6">
-        <v>59.22631701054202</v>
+        <v>59.54396285355087</v>
       </c>
       <c r="AP6">
         <v>1267.501466195757</v>
@@ -1276,7 +1276,7 @@
         <v>148.5381541341336</v>
       </c>
       <c r="AR6">
-        <v>90.43683677580486</v>
+        <v>89.89319123168221</v>
       </c>
       <c r="AS6">
         <v>11.73249902229175</v>
@@ -1301,10 +1301,10 @@
         <v>891.3051680874439</v>
       </c>
       <c r="C7">
-        <v>197.5892987764462</v>
+        <v>197.804165026258</v>
       </c>
       <c r="D7">
-        <v>4450.153661369418</v>
+        <v>4453.997943338089</v>
       </c>
       <c r="E7">
         <v>347.1796050403274</v>
@@ -1325,7 +1325,7 @@
         <v>81.04783096049411</v>
       </c>
       <c r="K7">
-        <v>5.669201301803542E-15</v>
+        <v>5.369110955731711E-15</v>
       </c>
       <c r="L7">
         <v>2276.069101684627</v>
@@ -1388,7 +1388,7 @@
         <v>0.295735790808919</v>
       </c>
       <c r="AH7">
-        <v>1152.882486318862</v>
+        <v>1154.801749975303</v>
       </c>
       <c r="AJ7">
         <v>25.20471970857072</v>
@@ -1585,46 +1585,46 @@
         </is>
       </c>
       <c r="B9">
-        <v>657.2683527566114</v>
+        <v>656.5532329749104</v>
       </c>
       <c r="C9">
-        <v>85.14539029535865</v>
+        <v>84.56427158615443</v>
       </c>
       <c r="D9">
-        <v>11201.99267112598</v>
+        <v>11203.36568936273</v>
       </c>
       <c r="E9">
-        <v>404.1195760715968</v>
+        <v>403.275164756447</v>
       </c>
       <c r="F9">
-        <v>606.4035453047776</v>
+        <v>605.3766352859135</v>
       </c>
       <c r="G9">
-        <v>30.25506168158294</v>
+        <v>29.96545324563912</v>
       </c>
       <c r="H9">
         <v>7.630503610722181</v>
       </c>
       <c r="I9">
-        <v>340.7338285548798</v>
+        <v>341.2620941929584</v>
       </c>
       <c r="J9">
-        <v>55.70274542429285</v>
+        <v>55.78828972158258</v>
       </c>
       <c r="K9">
-        <v>5.520453425025361E-15</v>
+        <v>5.494521193603784E-15</v>
       </c>
       <c r="L9">
-        <v>7187.304139642621</v>
+        <v>7190.945210132412</v>
       </c>
       <c r="M9">
-        <v>2781.964730384243</v>
+        <v>2759.463524766691</v>
       </c>
       <c r="N9">
-        <v>1060.743629523467</v>
+        <v>1060.901411554496</v>
       </c>
       <c r="O9">
-        <v>298.394415274463</v>
+        <v>297.9872974910394</v>
       </c>
       <c r="P9">
         <v>39.49272680010397</v>
@@ -1636,28 +1636,28 @@
         <v>3.204485111071812</v>
       </c>
       <c r="S9">
-        <v>29.35287661231341</v>
+        <v>29.16864244741702</v>
       </c>
       <c r="T9">
-        <v>46.03375039389823</v>
+        <v>45.86037858323198</v>
       </c>
       <c r="U9">
-        <v>67.3756381660471</v>
+        <v>67.42128205128205</v>
       </c>
       <c r="V9">
-        <v>146.82375</v>
+        <v>145.9542887249737</v>
       </c>
       <c r="W9">
-        <v>260.3667923151751</v>
+        <v>258.2691181364393</v>
       </c>
       <c r="Z9">
-        <v>2.340006468883112E-14</v>
+        <v>2.324180911021413E-14</v>
       </c>
       <c r="AA9">
         <v>10.70982877860762</v>
       </c>
       <c r="AB9">
-        <v>19.71559536360483</v>
+        <v>19.53983717496409</v>
       </c>
       <c r="AC9">
         <v>7.587348998258752E-17</v>
@@ -1675,37 +1675,37 @@
         <v>0.5362524525833878</v>
       </c>
       <c r="AH9">
-        <v>5653.549132719421</v>
+        <v>5655.762794755376</v>
       </c>
       <c r="AJ9">
         <v>111.3280144524274</v>
       </c>
       <c r="AK9">
-        <v>664.5288316272503</v>
+        <v>664.6797428189712</v>
       </c>
       <c r="AL9">
-        <v>105.2837213986881</v>
+        <v>105.3551414102154</v>
       </c>
       <c r="AM9">
-        <v>49.67909836065574</v>
+        <v>50.13491651828679</v>
       </c>
       <c r="AN9">
-        <v>58.06531453843269</v>
+        <v>58.13839507278321</v>
       </c>
       <c r="AO9">
-        <v>104.6646471054731</v>
+        <v>106.1923838818826</v>
       </c>
       <c r="AP9">
-        <v>2061.439374649308</v>
+        <v>2054.408342484441</v>
       </c>
       <c r="AQ9">
-        <v>160.8551168139742</v>
+        <v>160.4920520117882</v>
       </c>
       <c r="AR9">
-        <v>141.6772164009112</v>
+        <v>140.2478499029545</v>
       </c>
       <c r="AS9">
-        <v>20.86247018610833</v>
+        <v>20.79562436561933</v>
       </c>
       <c r="AT9">
         <v>4.672601164551887</v>

--- a/base_datas/mediana_porte_detalhamento.xlsx
+++ b/base_datas/mediana_porte_detalhamento.xlsx
@@ -603,133 +603,133 @@
         </is>
       </c>
       <c r="B2">
-        <v>450.6256326690304</v>
+        <v>456.8052171301064</v>
       </c>
       <c r="C2">
-        <v>93.85868977928376</v>
+        <v>94.31042408685016</v>
       </c>
       <c r="D2">
-        <v>6160.006504565668</v>
+        <v>6161.294600689007</v>
       </c>
       <c r="E2">
-        <v>203.6991251476329</v>
+        <v>203.7636758271807</v>
       </c>
       <c r="F2">
-        <v>417.6053922671344</v>
+        <v>419.6955285812672</v>
       </c>
       <c r="G2">
-        <v>26.74412764194565</v>
+        <v>26.79082506422203</v>
       </c>
       <c r="H2">
-        <v>2.464289194246486</v>
+        <v>2.44279792746114</v>
       </c>
       <c r="I2">
-        <v>193.6979540567158</v>
+        <v>194.5469730910116</v>
       </c>
       <c r="J2">
         <v>54.05462622262287</v>
       </c>
       <c r="K2">
-        <v>6.542456719352234E-15</v>
+        <v>6.521866769015956E-15</v>
       </c>
       <c r="L2">
-        <v>3668.231330543728</v>
+        <v>3671.029392642839</v>
       </c>
       <c r="M2">
-        <v>1198.665492033857</v>
+        <v>1204.829392165691</v>
       </c>
       <c r="N2">
-        <v>1038.276592869498</v>
+        <v>1038.575232673646</v>
       </c>
       <c r="O2">
-        <v>133.3601325301205</v>
+        <v>133.5732065940366</v>
       </c>
       <c r="P2">
-        <v>10.33738650999623</v>
+        <v>10.5693961830617</v>
       </c>
       <c r="Q2">
-        <v>0.5236530226073101</v>
+        <v>0.4984936514551702</v>
       </c>
       <c r="R2">
         <v>7.332765104418089</v>
       </c>
       <c r="S2">
-        <v>22.99870697543174</v>
+        <v>23.01537716715766</v>
       </c>
       <c r="T2">
-        <v>26.4244898336414</v>
+        <v>27.14053595953406</v>
       </c>
       <c r="U2">
-        <v>26.703024573251</v>
+        <v>27.06993996826654</v>
       </c>
       <c r="V2">
-        <v>145.6032552932305</v>
+        <v>146.2342165631187</v>
       </c>
       <c r="W2">
-        <v>172.5681165708563</v>
+        <v>172.7555519555659</v>
       </c>
       <c r="Z2">
-        <v>1.580777606904791E-14</v>
+        <v>1.57042117667523E-14</v>
       </c>
       <c r="AA2">
-        <v>12.78764122217556</v>
+        <v>12.70860236705915</v>
       </c>
       <c r="AB2">
-        <v>14.34896476224583</v>
+        <v>14.44503481508766</v>
       </c>
       <c r="AC2">
-        <v>8.818282974494701E-17</v>
+        <v>1.133679902490406E-16</v>
       </c>
       <c r="AD2">
-        <v>1.116777786746307</v>
+        <v>1.037030797101449</v>
       </c>
       <c r="AE2">
-        <v>8.000536172695449</v>
+        <v>8.853856460638839</v>
       </c>
       <c r="AF2">
         <v>27.7285557212076</v>
       </c>
       <c r="AG2">
-        <v>0.2170091418460631</v>
+        <v>0.2177627074897195</v>
       </c>
       <c r="AH2">
-        <v>2270.069233558672</v>
+        <v>2274.423401747882</v>
       </c>
       <c r="AJ2">
-        <v>43.97884586768421</v>
+        <v>43.98790602108272</v>
       </c>
       <c r="AK2">
-        <v>630.9461879494374</v>
+        <v>630.4247320461352</v>
       </c>
       <c r="AL2">
-        <v>116.7171192429247</v>
+        <v>116.7422103556785</v>
       </c>
       <c r="AM2">
-        <v>222.4197080774844</v>
+        <v>220.41225745206</v>
       </c>
       <c r="AN2">
-        <v>28.53491282957244</v>
+        <v>28.48400306997056</v>
       </c>
       <c r="AO2">
-        <v>50.82110666362606</v>
+        <v>51.04342032892968</v>
       </c>
       <c r="AP2">
-        <v>835.275786531667</v>
+        <v>835.4487473987347</v>
       </c>
       <c r="AQ2">
-        <v>82.37278227755047</v>
+        <v>83.30802230242037</v>
       </c>
       <c r="AR2">
-        <v>55.19440006139949</v>
+        <v>55.26116707078228</v>
       </c>
       <c r="AS2">
-        <v>9.938647058136137</v>
+        <v>9.935197282466683</v>
       </c>
       <c r="AT2">
         <v>3.748675733715104</v>
       </c>
       <c r="AU2">
-        <v>84.344921469453</v>
+        <v>84.70313406351686</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -742,46 +742,46 @@
         </is>
       </c>
       <c r="B3">
-        <v>1151.697488855529</v>
+        <v>1147.647611721434</v>
       </c>
       <c r="C3">
-        <v>229.2950446271612</v>
+        <v>228.0856205795863</v>
       </c>
       <c r="D3">
-        <v>3943.36987080005</v>
+        <v>3931.003989683961</v>
       </c>
       <c r="E3">
-        <v>444.7050963348964</v>
+        <v>439.214179733445</v>
       </c>
       <c r="F3">
-        <v>1021.207905932012</v>
+        <v>1013.232356311615</v>
       </c>
       <c r="G3">
         <v>79.58381908443897</v>
       </c>
       <c r="H3">
-        <v>0.5193485026561986</v>
+        <v>0.5180636711062901</v>
       </c>
       <c r="I3">
-        <v>157.2140538182077</v>
+        <v>156.2716555857762</v>
       </c>
       <c r="J3">
-        <v>88.03507828112672</v>
+        <v>88.2848482646687</v>
       </c>
       <c r="K3">
-        <v>-5.392937609604782E-15</v>
+        <v>-5.096017852569286E-15</v>
       </c>
       <c r="L3">
-        <v>1828.040776081521</v>
+        <v>1827.630779564254</v>
       </c>
       <c r="M3">
-        <v>1179.783139226421</v>
+        <v>1178.68281687783</v>
       </c>
       <c r="N3">
-        <v>809.0276161597283</v>
+        <v>809.1895796967893</v>
       </c>
       <c r="O3">
-        <v>213.6648455737482</v>
+        <v>209.6474237182563</v>
       </c>
       <c r="P3">
         <v>19.31889854378154</v>
@@ -793,34 +793,34 @@
         <v>1.907603964804308</v>
       </c>
       <c r="S3">
-        <v>98.88162806599524</v>
+        <v>96.12903027292657</v>
       </c>
       <c r="T3">
-        <v>245.0038390182517</v>
+        <v>241.9893683254195</v>
       </c>
       <c r="U3">
         <v>87.63185848747365</v>
       </c>
       <c r="V3">
-        <v>401.3171496322813</v>
+        <v>400.2408040363246</v>
       </c>
       <c r="W3">
-        <v>224.234212003079</v>
+        <v>223.2068780457181</v>
       </c>
       <c r="Z3">
-        <v>1.786744253348704E-14</v>
+        <v>1.501599823540043E-14</v>
       </c>
       <c r="AA3">
-        <v>33.75429208975805</v>
+        <v>33.80549900875715</v>
       </c>
       <c r="AB3">
-        <v>44.29964367913524</v>
+        <v>44.98823237315375</v>
       </c>
       <c r="AC3">
-        <v>-8.94031958376621E-16</v>
+        <v>-8.036457646879711E-16</v>
       </c>
       <c r="AD3">
-        <v>0.318141573043313</v>
+        <v>0.2991744770552943</v>
       </c>
       <c r="AE3">
         <v>2.006940626276107</v>
@@ -832,16 +832,16 @@
         <v>0.09331548013676666</v>
       </c>
       <c r="AH3">
-        <v>942.7559345996278</v>
+        <v>940.6839533742919</v>
       </c>
       <c r="AJ3">
-        <v>24.16460223138653</v>
+        <v>24.32261728719821</v>
       </c>
       <c r="AK3">
         <v>475.0941768305947</v>
       </c>
       <c r="AL3">
-        <v>76.73700512961436</v>
+        <v>76.87468518865045</v>
       </c>
       <c r="AM3">
         <v>28.63272351474025</v>
@@ -850,25 +850,25 @@
         <v>12.14586612392583</v>
       </c>
       <c r="AO3">
-        <v>19.8401654264599</v>
+        <v>19.40583099832969</v>
       </c>
       <c r="AP3">
         <v>766.8603074847499</v>
       </c>
       <c r="AQ3">
-        <v>213.7064350395914</v>
+        <v>213.5049392633443</v>
       </c>
       <c r="AR3">
-        <v>69.17810064424573</v>
+        <v>66.86292147758216</v>
       </c>
       <c r="AS3">
         <v>5.473453749315818</v>
       </c>
       <c r="AT3">
-        <v>2.376402405279721</v>
+        <v>2.384712271618399</v>
       </c>
       <c r="AU3">
-        <v>44.07059171268155</v>
+        <v>43.54038668085465</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -881,133 +881,133 @@
         </is>
       </c>
       <c r="B4">
-        <v>583.6242487943942</v>
+        <v>580.386420385051</v>
       </c>
       <c r="C4">
-        <v>124.0111320595555</v>
+        <v>124.8018128491161</v>
       </c>
       <c r="D4">
         <v>5232.048112211221</v>
       </c>
       <c r="E4">
-        <v>231.7837004548408</v>
+        <v>230.7162991983168</v>
       </c>
       <c r="F4">
-        <v>520.2307359202779</v>
+        <v>518.2245071081182</v>
       </c>
       <c r="G4">
-        <v>38.30543527071195</v>
+        <v>38.22514492373747</v>
       </c>
       <c r="H4">
-        <v>1.05080322702753</v>
+        <v>0.9839431652480586</v>
       </c>
       <c r="I4">
-        <v>187.9667100737101</v>
+        <v>188.6548454394294</v>
       </c>
       <c r="J4">
-        <v>66.01950500935814</v>
+        <v>66.40653266897502</v>
       </c>
       <c r="K4">
-        <v>6.352467632158398E-15</v>
+        <v>6.427150370866544E-15</v>
       </c>
       <c r="L4">
-        <v>3020.004460313193</v>
+        <v>3020.398339020229</v>
       </c>
       <c r="M4">
-        <v>1120.83774184834</v>
+        <v>1119.91407261957</v>
       </c>
       <c r="N4">
-        <v>977.0115791949789</v>
+        <v>978.8122197183047</v>
       </c>
       <c r="O4">
         <v>135.3977475710441</v>
       </c>
       <c r="P4">
-        <v>11.49564814003266</v>
+        <v>11.62278054391974</v>
       </c>
       <c r="Q4">
-        <v>0.7357870518609986</v>
+        <v>0.8105006954102921</v>
       </c>
       <c r="R4">
         <v>6.657107266695567</v>
       </c>
       <c r="S4">
-        <v>34.07317088286418</v>
+        <v>33.64501094777414</v>
       </c>
       <c r="T4">
-        <v>65.59527172763798</v>
+        <v>65.35693118091348</v>
       </c>
       <c r="U4">
-        <v>39.0331010994409</v>
+        <v>38.87635186936825</v>
       </c>
       <c r="V4">
-        <v>195.0747659498717</v>
+        <v>197.1188569344294</v>
       </c>
       <c r="W4">
-        <v>181.7019049196011</v>
+        <v>182.1734382069369</v>
       </c>
       <c r="Z4">
-        <v>1.948425238244579E-14</v>
+        <v>1.943819032007594E-14</v>
       </c>
       <c r="AA4">
         <v>19.61055887531345</v>
       </c>
       <c r="AB4">
-        <v>15.12169004693073</v>
+        <v>15.11280281375059</v>
       </c>
       <c r="AC4">
-        <v>-3.290819308807874E-17</v>
+        <v>-3.428732599056737E-17</v>
       </c>
       <c r="AD4">
-        <v>0.7809675478866551</v>
+        <v>0.7552765047539882</v>
       </c>
       <c r="AE4">
-        <v>0.2732647625291972</v>
+        <v>0.2426351921111595</v>
       </c>
       <c r="AF4">
-        <v>27.29024809152821</v>
+        <v>28.39939251345966</v>
       </c>
       <c r="AG4">
-        <v>0.1145514632476978</v>
+        <v>0.1117478923236208</v>
       </c>
       <c r="AH4">
-        <v>1637.631278806614</v>
+        <v>1636.375904583421</v>
       </c>
       <c r="AJ4">
         <v>34.06684321123263</v>
       </c>
       <c r="AK4">
-        <v>573.9121039858803</v>
+        <v>573.89764619011</v>
       </c>
       <c r="AL4">
-        <v>111.3065775303098</v>
+        <v>111.3839913608092</v>
       </c>
       <c r="AM4">
-        <v>223.0083036835496</v>
+        <v>226.1456490372054</v>
       </c>
       <c r="AN4">
-        <v>23.78472302960183</v>
+        <v>23.76877110530896</v>
       </c>
       <c r="AO4">
-        <v>37.31255486423841</v>
+        <v>37.99963305581243</v>
       </c>
       <c r="AP4">
-        <v>706.1995342774608</v>
+        <v>704.9803686393028</v>
       </c>
       <c r="AQ4">
-        <v>110.2971352872312</v>
+        <v>110.1496161609506</v>
       </c>
       <c r="AR4">
         <v>52.12223544712884</v>
       </c>
       <c r="AS4">
-        <v>8.090145085803432</v>
+        <v>8.108818213568497</v>
       </c>
       <c r="AT4">
-        <v>4.242347816781932</v>
+        <v>4.035897375728421</v>
       </c>
       <c r="AU4">
-        <v>68.13251346564036</v>
+        <v>67.9829424124059</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1159,49 +1159,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>523.6222290747421</v>
+        <v>526.5314636189564</v>
       </c>
       <c r="C6">
-        <v>84.36839850295289</v>
+        <v>84.44091281727889</v>
       </c>
       <c r="D6">
-        <v>7154.229862351052</v>
+        <v>7157.146043080556</v>
       </c>
       <c r="E6">
-        <v>256.471443954926</v>
+        <v>256.1347072599531</v>
       </c>
       <c r="F6">
-        <v>467.2377202102275</v>
+        <v>468.7756277561608</v>
       </c>
       <c r="G6">
         <v>31.65709835856308</v>
       </c>
       <c r="H6">
-        <v>4.485234944788139</v>
+        <v>4.497896714922049</v>
       </c>
       <c r="I6">
-        <v>227.5981179885025</v>
+        <v>229.0581719642595</v>
       </c>
       <c r="J6">
-        <v>54.81680948687411</v>
+        <v>54.8072395658442</v>
       </c>
       <c r="K6">
-        <v>7.146073431570305E-15</v>
+        <v>7.046079277746932E-15</v>
       </c>
       <c r="L6">
-        <v>4194.763232427769</v>
+        <v>4201.715857294995</v>
       </c>
       <c r="M6">
-        <v>1754.655872245822</v>
+        <v>1751.127656273764</v>
       </c>
       <c r="N6">
-        <v>1014.167335362479</v>
+        <v>1014.590657361744</v>
       </c>
       <c r="O6">
-        <v>174.5055130731807</v>
+        <v>173.9627034207904</v>
       </c>
       <c r="P6">
-        <v>17.44562173331713</v>
+        <v>17.33197194076384</v>
       </c>
       <c r="Q6">
         <v>2.999543751511336</v>
@@ -1210,31 +1210,31 @@
         <v>9.454290137911215</v>
       </c>
       <c r="S6">
-        <v>22.82782238305218</v>
+        <v>22.85902871987265</v>
       </c>
       <c r="T6">
-        <v>40.19492581919095</v>
+        <v>39.71650141649322</v>
       </c>
       <c r="U6">
-        <v>49.26645631769541</v>
+        <v>49.30399871134021</v>
       </c>
       <c r="V6">
-        <v>149.0587425950698</v>
+        <v>149.718434657788</v>
       </c>
       <c r="W6">
-        <v>176.9724412206224</v>
+        <v>176.7738705567588</v>
       </c>
       <c r="Z6">
         <v>1.611285502847868E-14</v>
       </c>
       <c r="AA6">
-        <v>11.74109880289519</v>
+        <v>11.84817621908907</v>
       </c>
       <c r="AB6">
-        <v>19.06558734423207</v>
+        <v>19.01871619384096</v>
       </c>
       <c r="AC6">
-        <v>-1.542635869397706E-17</v>
+        <v>-3.980631572885715E-18</v>
       </c>
       <c r="AD6">
         <v>2.713943778512221</v>
@@ -1243,40 +1243,40 @@
         <v>6.370504097726922</v>
       </c>
       <c r="AF6">
-        <v>33.46588557345914</v>
+        <v>34.20417873651772</v>
       </c>
       <c r="AG6">
         <v>0.441501789781972</v>
       </c>
       <c r="AH6">
-        <v>2798.072175975</v>
+        <v>2798.386954296806</v>
       </c>
       <c r="AJ6">
-        <v>54.68343238668422</v>
+        <v>54.83812333875062</v>
       </c>
       <c r="AK6">
-        <v>621.5323996649465</v>
+        <v>622.4020116116546</v>
       </c>
       <c r="AL6">
-        <v>106.5805140286088</v>
+        <v>106.778398334794</v>
       </c>
       <c r="AM6">
-        <v>71.8504468738013</v>
+        <v>72.03521308576481</v>
       </c>
       <c r="AN6">
-        <v>36.91147952663471</v>
+        <v>37.13522202562716</v>
       </c>
       <c r="AO6">
-        <v>59.22631701054202</v>
+        <v>59.69762528912883</v>
       </c>
       <c r="AP6">
-        <v>1267.501466195757</v>
+        <v>1266.370360533226</v>
       </c>
       <c r="AQ6">
-        <v>148.5381541341336</v>
+        <v>148.1328383045526</v>
       </c>
       <c r="AR6">
-        <v>90.43683677580486</v>
+        <v>89.8928423914215</v>
       </c>
       <c r="AS6">
         <v>11.73249902229175</v>
@@ -1285,7 +1285,7 @@
         <v>3.924270139309509</v>
       </c>
       <c r="AU6">
-        <v>132.6223932825442</v>
+        <v>132.5610601032449</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1301,10 +1301,10 @@
         <v>891.3051680874439</v>
       </c>
       <c r="C7">
-        <v>197.5892987764462</v>
+        <v>197.804165026258</v>
       </c>
       <c r="D7">
-        <v>4450.153661369418</v>
+        <v>4453.997943338089</v>
       </c>
       <c r="E7">
         <v>347.1796050403274</v>
@@ -1325,7 +1325,7 @@
         <v>81.04783096049411</v>
       </c>
       <c r="K7">
-        <v>5.669201301803542E-15</v>
+        <v>5.369110955731711E-15</v>
       </c>
       <c r="L7">
         <v>2276.069101684627</v>
@@ -1388,7 +1388,7 @@
         <v>0.295735790808919</v>
       </c>
       <c r="AH7">
-        <v>1152.882486318862</v>
+        <v>1154.801749975303</v>
       </c>
       <c r="AJ7">
         <v>25.20471970857072</v>
@@ -1585,46 +1585,46 @@
         </is>
       </c>
       <c r="B9">
-        <v>657.2683527566114</v>
+        <v>656.5532329749104</v>
       </c>
       <c r="C9">
-        <v>85.14539029535865</v>
+        <v>84.56427158615443</v>
       </c>
       <c r="D9">
-        <v>11201.99267112598</v>
+        <v>11203.36568936273</v>
       </c>
       <c r="E9">
-        <v>404.1195760715968</v>
+        <v>403.275164756447</v>
       </c>
       <c r="F9">
-        <v>606.4035453047776</v>
+        <v>605.3766352859135</v>
       </c>
       <c r="G9">
-        <v>30.25506168158294</v>
+        <v>29.96545324563912</v>
       </c>
       <c r="H9">
         <v>7.630503610722181</v>
       </c>
       <c r="I9">
-        <v>340.7338285548798</v>
+        <v>341.2620941929584</v>
       </c>
       <c r="J9">
-        <v>55.70274542429285</v>
+        <v>55.78828972158258</v>
       </c>
       <c r="K9">
-        <v>5.520453425025361E-15</v>
+        <v>5.494521193603784E-15</v>
       </c>
       <c r="L9">
-        <v>7187.304139642621</v>
+        <v>7190.945210132412</v>
       </c>
       <c r="M9">
-        <v>2781.964730384243</v>
+        <v>2759.463524766691</v>
       </c>
       <c r="N9">
-        <v>1060.743629523467</v>
+        <v>1060.901411554496</v>
       </c>
       <c r="O9">
-        <v>298.394415274463</v>
+        <v>297.9872974910394</v>
       </c>
       <c r="P9">
         <v>39.49272680010397</v>
@@ -1636,28 +1636,28 @@
         <v>3.204485111071812</v>
       </c>
       <c r="S9">
-        <v>29.35287661231341</v>
+        <v>29.16864244741702</v>
       </c>
       <c r="T9">
-        <v>46.03375039389823</v>
+        <v>45.86037858323198</v>
       </c>
       <c r="U9">
-        <v>67.3756381660471</v>
+        <v>67.42128205128205</v>
       </c>
       <c r="V9">
-        <v>146.82375</v>
+        <v>145.9542887249737</v>
       </c>
       <c r="W9">
-        <v>260.3667923151751</v>
+        <v>258.2691181364393</v>
       </c>
       <c r="Z9">
-        <v>2.340006468883112E-14</v>
+        <v>2.324180911021413E-14</v>
       </c>
       <c r="AA9">
         <v>10.70982877860762</v>
       </c>
       <c r="AB9">
-        <v>19.71559536360483</v>
+        <v>19.53983717496409</v>
       </c>
       <c r="AC9">
         <v>7.587348998258752E-17</v>
@@ -1675,37 +1675,37 @@
         <v>0.5362524525833878</v>
       </c>
       <c r="AH9">
-        <v>5653.549132719421</v>
+        <v>5655.762794755376</v>
       </c>
       <c r="AJ9">
         <v>111.3280144524274</v>
       </c>
       <c r="AK9">
-        <v>664.5288316272503</v>
+        <v>664.6797428189712</v>
       </c>
       <c r="AL9">
-        <v>105.2837213986881</v>
+        <v>105.3551414102154</v>
       </c>
       <c r="AM9">
-        <v>49.67909836065574</v>
+        <v>50.13491651828679</v>
       </c>
       <c r="AN9">
-        <v>58.06531453843269</v>
+        <v>58.13839507278321</v>
       </c>
       <c r="AO9">
-        <v>104.6646471054731</v>
+        <v>106.1923838818826</v>
       </c>
       <c r="AP9">
-        <v>2061.439374649308</v>
+        <v>2054.408342484441</v>
       </c>
       <c r="AQ9">
-        <v>160.8551168139742</v>
+        <v>160.4920520117882</v>
       </c>
       <c r="AR9">
-        <v>141.6772164009112</v>
+        <v>140.2478499029545</v>
       </c>
       <c r="AS9">
-        <v>20.86247018610833</v>
+        <v>20.79562436561933</v>
       </c>
       <c r="AT9">
         <v>4.672601164551887</v>
